--- a/Book1.xlsx
+++ b/Book1.xlsx
@@ -5,18 +5,22 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Julius Calabano\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Julius Calabano\Documents\CSTC Compilation Files\1st SEM AY 2026-2027\MAS3 - BSAIS-BSBA\Finals\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1BB55A85-ED16-4951-8632-F72BB8BA7100}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C03F061-FE74-4BE4-B2A1-45F1BC6961BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{5B656E91-301E-4821-8536-BF582F2D3F38}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
-    <sheet name="Sheet4" sheetId="4" r:id="rId4"/>
+    <sheet name="Names" sheetId="1" r:id="rId1"/>
+    <sheet name="Blank" sheetId="2" r:id="rId2"/>
+    <sheet name="Grades" sheetId="3" r:id="rId3"/>
+    <sheet name="Records" sheetId="4" r:id="rId4"/>
+    <sheet name="Comparison Operators" sheetId="5" r:id="rId5"/>
+    <sheet name="Concatenation Operators" sheetId="6" r:id="rId6"/>
+    <sheet name="Reference Operator" sheetId="7" r:id="rId7"/>
+    <sheet name="Filter Function" sheetId="8" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="115">
   <si>
     <t>Student</t>
   </si>
@@ -238,13 +242,282 @@
   </si>
   <si>
     <t>Zhaira Erica</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">In MS-Excel formulas, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Comparison, or Logical operators </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>are used to comparing two values. The result of the comparison is always a logical value of True or False.</t>
+    </r>
+  </si>
+  <si>
+    <t>FORMULA: =A1 =B1</t>
+  </si>
+  <si>
+    <t>DATA SAMPLE 1</t>
+  </si>
+  <si>
+    <t>DATA SAMPLE 2</t>
+  </si>
+  <si>
+    <t>DATA RESULT</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Text </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Concatination Operator</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> in Excel is the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Ampersand Symbol (&amp;).</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> You can use it to join two or more text strings in a single string.</t>
+    </r>
+  </si>
+  <si>
+    <t>Formula: =A1&amp;" "&amp;B1</t>
+  </si>
+  <si>
+    <t>LASTNAME</t>
+  </si>
+  <si>
+    <t>FIRSTNAME</t>
+  </si>
+  <si>
+    <t>MI.</t>
+  </si>
+  <si>
+    <t>FULLNAME</t>
+  </si>
+  <si>
+    <t>CREDO</t>
+  </si>
+  <si>
+    <t>BRIAN ARLOU</t>
+  </si>
+  <si>
+    <t>L.</t>
+  </si>
+  <si>
+    <r>
+      <t>Colon (:)</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>- it is a range operator that allows you to make one reference for multiple cells located between 2 cells that you specify</t>
+    </r>
+  </si>
+  <si>
+    <t>DATA 1</t>
+  </si>
+  <si>
+    <t>DATA 2</t>
+  </si>
+  <si>
+    <t>DATA 3</t>
+  </si>
+  <si>
+    <t>DATA 4</t>
+  </si>
+  <si>
+    <t>TOTAL</t>
+  </si>
+  <si>
+    <t>AVG</t>
+  </si>
+  <si>
+    <t>Formula: =SUM(A1:D1)</t>
+  </si>
+  <si>
+    <r>
+      <t>Comma (,)</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>- is used to separate arguments or parameters in Excel functions and formulas.</t>
+    </r>
+  </si>
+  <si>
+    <t>RESULT</t>
+  </si>
+  <si>
+    <t>Formula: SUM(A1,B1,C1,D1)</t>
+  </si>
+  <si>
+    <r>
+      <t>Spaces</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> - are not operators in the traditional sense but are used to separate elements within a formula for easier comprehension.</t>
+    </r>
+  </si>
+  <si>
+    <t>Formula: =A1:D1 C2:C4</t>
+  </si>
+  <si>
+    <t>BSIT</t>
+  </si>
+  <si>
+    <t>Block 1</t>
+  </si>
+  <si>
+    <t>Block 2</t>
+  </si>
+  <si>
+    <t>Block 3</t>
+  </si>
+  <si>
+    <t>Block 4</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Block</t>
+  </si>
+  <si>
+    <t>Sarah Johnson</t>
+  </si>
+  <si>
+    <t>Michael Smith</t>
+  </si>
+  <si>
+    <t>Emily Davis</t>
+  </si>
+  <si>
+    <t>Daniel Brown</t>
+  </si>
+  <si>
+    <t>Olivia Wilson</t>
+  </si>
+  <si>
+    <t>James Anderson</t>
+  </si>
+  <si>
+    <t>Sophia Martin</t>
+  </si>
+  <si>
+    <t>William Lee</t>
+  </si>
+  <si>
+    <t>Ava Robinson</t>
+  </si>
+  <si>
+    <t>Benjamin Taylor</t>
+  </si>
+  <si>
+    <t>Mia Clark</t>
+  </si>
+  <si>
+    <t>Ethan Turner</t>
+  </si>
+  <si>
+    <t>Isabella White</t>
+  </si>
+  <si>
+    <t>FILTER(I6:I18,J6:J18="Block 1")</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -260,16 +533,89 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF00B050"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF0CC07B"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial Narrow"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF0CC07B"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7F7F7F"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="31">
     <border>
       <left/>
       <right/>
@@ -277,11 +623,377 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thick">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thick">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thick">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thick">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thick">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thick">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="thick">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="thick">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thick">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thick">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="thick">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="thick">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="thick">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="thick">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thick">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thick">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thick">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thick">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thick">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thick">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thick">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -291,6 +1003,166 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1126,4 +1998,718 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E278F978-3AEC-4C38-A58B-B2957709252A}">
+  <dimension ref="A1:C8"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:3" ht="71.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="B1" s="12"/>
+      <c r="C1" s="13"/>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" s="14"/>
+      <c r="B2" s="15"/>
+      <c r="C2" s="16"/>
+    </row>
+    <row r="3" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="17"/>
+      <c r="B3" s="18"/>
+      <c r="C3" s="19"/>
+    </row>
+    <row r="4" spans="1:3" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="B4" s="21"/>
+      <c r="C4" s="22"/>
+    </row>
+    <row r="5" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="5"/>
+      <c r="B5" s="5"/>
+      <c r="C5" s="5"/>
+    </row>
+    <row r="6" spans="1:3" ht="54.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="8">
+        <v>100</v>
+      </c>
+      <c r="B7" s="9">
+        <v>100</v>
+      </c>
+      <c r="C7" s="10"/>
+    </row>
+    <row r="8" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="8">
+        <v>50</v>
+      </c>
+      <c r="B8" s="9">
+        <v>49</v>
+      </c>
+      <c r="C8" s="10"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C3"/>
+    <mergeCell ref="A4:C4"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09368F8F-DA2F-46D8-8EBA-14C093FC071C}">
+  <dimension ref="A1:E8"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="19.6640625" customWidth="1"/>
+    <col min="3" max="3" width="18.6640625" customWidth="1"/>
+    <col min="5" max="5" width="22.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="13"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="14"/>
+      <c r="B2" s="15"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="16"/>
+    </row>
+    <row r="3" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="17"/>
+      <c r="B3" s="18"/>
+      <c r="C3" s="18"/>
+      <c r="D3" s="18"/>
+      <c r="E3" s="19"/>
+    </row>
+    <row r="4" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="25" t="s">
+        <v>73</v>
+      </c>
+      <c r="B4" s="26"/>
+      <c r="C4" s="26"/>
+      <c r="D4" s="26"/>
+      <c r="E4" s="27"/>
+    </row>
+    <row r="5" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="5"/>
+      <c r="B5" s="5"/>
+      <c r="C5" s="5"/>
+      <c r="D5" s="5"/>
+      <c r="E5" s="5"/>
+    </row>
+    <row r="6" spans="1:5" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="23"/>
+      <c r="B6" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="23"/>
+      <c r="B7" s="24" t="s">
+        <v>78</v>
+      </c>
+      <c r="C7" s="24" t="s">
+        <v>79</v>
+      </c>
+      <c r="D7" s="24" t="s">
+        <v>80</v>
+      </c>
+      <c r="E7" s="24"/>
+    </row>
+    <row r="8" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="23"/>
+      <c r="B8" s="24"/>
+      <c r="C8" s="24"/>
+      <c r="D8" s="24"/>
+      <c r="E8" s="24"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:E3"/>
+    <mergeCell ref="A4:E4"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8CCA848-1B8C-4AD9-A1AE-41AF845A53C9}">
+  <dimension ref="A1:N14"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="2" spans="1:14" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="39" t="s">
+        <v>81</v>
+      </c>
+      <c r="B2" s="40"/>
+      <c r="C2" s="40"/>
+      <c r="D2" s="40"/>
+      <c r="E2" s="40"/>
+      <c r="F2" s="40"/>
+      <c r="G2" s="41"/>
+      <c r="H2" s="28"/>
+      <c r="I2" s="29" t="s">
+        <v>82</v>
+      </c>
+      <c r="J2" s="29" t="s">
+        <v>83</v>
+      </c>
+      <c r="K2" s="29" t="s">
+        <v>84</v>
+      </c>
+      <c r="L2" s="29" t="s">
+        <v>85</v>
+      </c>
+      <c r="M2" s="29" t="s">
+        <v>86</v>
+      </c>
+      <c r="N2" s="29" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="42"/>
+      <c r="B3" s="43"/>
+      <c r="C3" s="43"/>
+      <c r="D3" s="43"/>
+      <c r="E3" s="43"/>
+      <c r="F3" s="43"/>
+      <c r="G3" s="44"/>
+      <c r="H3" s="28"/>
+      <c r="I3" s="30">
+        <v>3</v>
+      </c>
+      <c r="J3" s="30">
+        <v>5</v>
+      </c>
+      <c r="K3" s="30">
+        <v>25</v>
+      </c>
+      <c r="L3" s="30">
+        <v>2</v>
+      </c>
+      <c r="M3" s="31"/>
+      <c r="N3" s="31"/>
+    </row>
+    <row r="4" spans="1:14" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="45" t="s">
+        <v>88</v>
+      </c>
+      <c r="B4" s="46"/>
+      <c r="C4" s="46"/>
+      <c r="D4" s="46"/>
+      <c r="E4" s="46"/>
+      <c r="F4" s="46"/>
+      <c r="G4" s="47"/>
+      <c r="H4" s="32"/>
+      <c r="I4" s="32"/>
+      <c r="J4" s="32"/>
+      <c r="K4" s="32"/>
+      <c r="L4" s="32"/>
+      <c r="M4" s="32"/>
+      <c r="N4" s="32"/>
+    </row>
+    <row r="5" spans="1:14" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="33"/>
+      <c r="B5" s="33"/>
+      <c r="C5" s="33"/>
+      <c r="D5" s="33"/>
+      <c r="E5" s="33"/>
+      <c r="F5" s="33"/>
+      <c r="G5" s="33"/>
+      <c r="H5" s="32"/>
+      <c r="I5" s="33"/>
+      <c r="J5" s="33"/>
+      <c r="K5" s="33"/>
+      <c r="L5" s="33"/>
+      <c r="M5" s="33"/>
+      <c r="N5" s="33"/>
+    </row>
+    <row r="6" spans="1:14" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="39" t="s">
+        <v>89</v>
+      </c>
+      <c r="B6" s="40"/>
+      <c r="C6" s="40"/>
+      <c r="D6" s="40"/>
+      <c r="E6" s="40"/>
+      <c r="F6" s="40"/>
+      <c r="G6" s="41"/>
+      <c r="H6" s="28"/>
+      <c r="I6" s="34" t="s">
+        <v>82</v>
+      </c>
+      <c r="J6" s="35" t="s">
+        <v>83</v>
+      </c>
+      <c r="K6" s="34" t="s">
+        <v>82</v>
+      </c>
+      <c r="L6" s="35" t="s">
+        <v>83</v>
+      </c>
+      <c r="M6" s="34" t="s">
+        <v>90</v>
+      </c>
+      <c r="N6" s="35" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="42"/>
+      <c r="B7" s="43"/>
+      <c r="C7" s="43"/>
+      <c r="D7" s="43"/>
+      <c r="E7" s="43"/>
+      <c r="F7" s="43"/>
+      <c r="G7" s="44"/>
+      <c r="H7" s="28"/>
+      <c r="I7" s="36">
+        <v>3</v>
+      </c>
+      <c r="J7" s="36">
+        <v>5</v>
+      </c>
+      <c r="K7" s="36">
+        <v>25</v>
+      </c>
+      <c r="L7" s="36">
+        <v>2</v>
+      </c>
+      <c r="M7" s="37"/>
+      <c r="N7" s="37"/>
+    </row>
+    <row r="8" spans="1:14" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="45" t="s">
+        <v>91</v>
+      </c>
+      <c r="B8" s="46"/>
+      <c r="C8" s="46"/>
+      <c r="D8" s="46"/>
+      <c r="E8" s="46"/>
+      <c r="F8" s="46"/>
+      <c r="G8" s="47"/>
+      <c r="H8" s="32"/>
+      <c r="I8" s="32"/>
+      <c r="J8" s="32"/>
+      <c r="K8" s="32"/>
+      <c r="L8" s="32"/>
+      <c r="M8" s="32"/>
+      <c r="N8" s="32"/>
+    </row>
+    <row r="9" spans="1:14" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="33"/>
+      <c r="B9" s="33"/>
+      <c r="C9" s="33"/>
+      <c r="D9" s="33"/>
+      <c r="E9" s="33"/>
+      <c r="F9" s="33"/>
+      <c r="G9" s="33"/>
+      <c r="H9" s="32"/>
+      <c r="I9" s="33"/>
+      <c r="J9" s="33"/>
+      <c r="K9" s="33"/>
+      <c r="L9" s="32"/>
+      <c r="M9" s="33"/>
+      <c r="N9" s="32"/>
+    </row>
+    <row r="10" spans="1:14" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="39" t="s">
+        <v>92</v>
+      </c>
+      <c r="B10" s="40"/>
+      <c r="C10" s="40"/>
+      <c r="D10" s="40"/>
+      <c r="E10" s="40"/>
+      <c r="F10" s="40"/>
+      <c r="G10" s="41"/>
+      <c r="H10" s="28"/>
+      <c r="I10" s="30">
+        <v>1</v>
+      </c>
+      <c r="J10" s="30">
+        <v>9</v>
+      </c>
+      <c r="K10" s="30">
+        <v>15</v>
+      </c>
+      <c r="L10" s="28"/>
+      <c r="M10" s="38" t="s">
+        <v>90</v>
+      </c>
+      <c r="N10" s="32"/>
+    </row>
+    <row r="11" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="42"/>
+      <c r="B11" s="43"/>
+      <c r="C11" s="43"/>
+      <c r="D11" s="43"/>
+      <c r="E11" s="43"/>
+      <c r="F11" s="43"/>
+      <c r="G11" s="44"/>
+      <c r="H11" s="28"/>
+      <c r="I11" s="30">
+        <v>6</v>
+      </c>
+      <c r="J11" s="30">
+        <v>2</v>
+      </c>
+      <c r="K11" s="30">
+        <v>10</v>
+      </c>
+      <c r="L11" s="28"/>
+      <c r="M11" s="31"/>
+      <c r="N11" s="32"/>
+    </row>
+    <row r="12" spans="1:14" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="45" t="s">
+        <v>93</v>
+      </c>
+      <c r="B12" s="46"/>
+      <c r="C12" s="46"/>
+      <c r="D12" s="46"/>
+      <c r="E12" s="46"/>
+      <c r="F12" s="46"/>
+      <c r="G12" s="47"/>
+      <c r="H12" s="28"/>
+      <c r="I12" s="30">
+        <v>11</v>
+      </c>
+      <c r="J12" s="30">
+        <v>7</v>
+      </c>
+      <c r="K12" s="30">
+        <v>3</v>
+      </c>
+      <c r="L12" s="32"/>
+      <c r="M12" s="32"/>
+      <c r="N12" s="32"/>
+    </row>
+    <row r="13" spans="1:14" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="32"/>
+      <c r="B13" s="32"/>
+      <c r="C13" s="32"/>
+      <c r="D13" s="32"/>
+      <c r="E13" s="32"/>
+      <c r="F13" s="32"/>
+      <c r="G13" s="32"/>
+      <c r="H13" s="28"/>
+      <c r="I13" s="30">
+        <v>12</v>
+      </c>
+      <c r="J13" s="30">
+        <v>4</v>
+      </c>
+      <c r="K13" s="30">
+        <v>8</v>
+      </c>
+      <c r="L13" s="32"/>
+      <c r="M13" s="32"/>
+      <c r="N13" s="32"/>
+    </row>
+    <row r="14" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="32"/>
+      <c r="B14" s="32"/>
+      <c r="C14" s="32"/>
+      <c r="D14" s="32"/>
+      <c r="E14" s="32"/>
+      <c r="F14" s="32"/>
+      <c r="G14" s="32"/>
+      <c r="H14" s="28"/>
+      <c r="I14" s="30">
+        <v>5</v>
+      </c>
+      <c r="J14" s="30">
+        <v>13</v>
+      </c>
+      <c r="K14" s="30">
+        <v>14</v>
+      </c>
+      <c r="L14" s="32"/>
+      <c r="M14" s="32"/>
+      <c r="N14" s="32"/>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A2:G3"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A6:G7"/>
+    <mergeCell ref="A8:G8"/>
+    <mergeCell ref="A10:G11"/>
+    <mergeCell ref="A12:G12"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4980B03-514A-40A0-A79D-98224B9A1AB1}">
+  <dimension ref="C3:J18"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="9" max="9" width="16.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="4" spans="3:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C4" s="53" t="s">
+        <v>94</v>
+      </c>
+      <c r="D4" s="54"/>
+      <c r="E4" s="54"/>
+      <c r="F4" s="55"/>
+      <c r="G4" s="32"/>
+      <c r="H4" s="48"/>
+      <c r="I4" s="56" t="s">
+        <v>94</v>
+      </c>
+      <c r="J4" s="57"/>
+    </row>
+    <row r="5" spans="3:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C5" s="49" t="s">
+        <v>95</v>
+      </c>
+      <c r="D5" s="50" t="s">
+        <v>96</v>
+      </c>
+      <c r="E5" s="50" t="s">
+        <v>97</v>
+      </c>
+      <c r="F5" s="50" t="s">
+        <v>98</v>
+      </c>
+      <c r="G5" s="32"/>
+      <c r="H5" s="48"/>
+      <c r="I5" s="50" t="s">
+        <v>99</v>
+      </c>
+      <c r="J5" s="50" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C6" s="58" t="s">
+        <v>114</v>
+      </c>
+      <c r="D6" s="52"/>
+      <c r="E6" s="52"/>
+      <c r="F6" s="52"/>
+      <c r="G6" s="32"/>
+      <c r="H6" s="48"/>
+      <c r="I6" s="52" t="s">
+        <v>101</v>
+      </c>
+      <c r="J6" s="52" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="7" spans="3:10" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C7" s="51"/>
+      <c r="D7" s="52"/>
+      <c r="E7" s="52"/>
+      <c r="F7" s="52"/>
+      <c r="G7" s="32"/>
+      <c r="H7" s="48"/>
+      <c r="I7" s="52" t="s">
+        <v>102</v>
+      </c>
+      <c r="J7" s="52" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="8" spans="3:10" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C8" s="51"/>
+      <c r="D8" s="52"/>
+      <c r="E8" s="52"/>
+      <c r="F8" s="52"/>
+      <c r="G8" s="32"/>
+      <c r="H8" s="48"/>
+      <c r="I8" s="52" t="s">
+        <v>103</v>
+      </c>
+      <c r="J8" s="52" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="9" spans="3:10" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C9" s="51"/>
+      <c r="D9" s="52"/>
+      <c r="E9" s="52"/>
+      <c r="F9" s="52"/>
+      <c r="G9" s="32"/>
+      <c r="H9" s="48"/>
+      <c r="I9" s="52" t="s">
+        <v>104</v>
+      </c>
+      <c r="J9" s="52" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="10" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C10" s="51"/>
+      <c r="D10" s="52"/>
+      <c r="E10" s="52"/>
+      <c r="F10" s="52"/>
+      <c r="G10" s="32"/>
+      <c r="H10" s="48"/>
+      <c r="I10" s="52" t="s">
+        <v>105</v>
+      </c>
+      <c r="J10" s="52" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="11" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C11" s="51"/>
+      <c r="D11" s="52"/>
+      <c r="E11" s="52"/>
+      <c r="F11" s="52"/>
+      <c r="G11" s="32"/>
+      <c r="H11" s="48"/>
+      <c r="I11" s="52" t="s">
+        <v>106</v>
+      </c>
+      <c r="J11" s="52" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="12" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C12" s="51"/>
+      <c r="D12" s="52"/>
+      <c r="E12" s="52"/>
+      <c r="F12" s="52"/>
+      <c r="G12" s="32"/>
+      <c r="H12" s="48"/>
+      <c r="I12" s="52" t="s">
+        <v>107</v>
+      </c>
+      <c r="J12" s="52" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="13" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C13" s="51"/>
+      <c r="D13" s="52"/>
+      <c r="E13" s="52"/>
+      <c r="F13" s="52"/>
+      <c r="G13" s="32"/>
+      <c r="H13" s="48"/>
+      <c r="I13" s="52" t="s">
+        <v>108</v>
+      </c>
+      <c r="J13" s="52" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="14" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C14" s="51"/>
+      <c r="D14" s="52"/>
+      <c r="E14" s="52"/>
+      <c r="F14" s="52"/>
+      <c r="G14" s="32"/>
+      <c r="H14" s="48"/>
+      <c r="I14" s="52" t="s">
+        <v>109</v>
+      </c>
+      <c r="J14" s="52" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="15" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C15" s="51"/>
+      <c r="D15" s="52"/>
+      <c r="E15" s="52"/>
+      <c r="F15" s="52"/>
+      <c r="G15" s="32"/>
+      <c r="H15" s="48"/>
+      <c r="I15" s="52" t="s">
+        <v>110</v>
+      </c>
+      <c r="J15" s="52" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="16" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C16" s="51"/>
+      <c r="D16" s="52"/>
+      <c r="E16" s="52"/>
+      <c r="F16" s="52"/>
+      <c r="G16" s="32"/>
+      <c r="H16" s="48"/>
+      <c r="I16" s="52" t="s">
+        <v>111</v>
+      </c>
+      <c r="J16" s="52" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="17" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C17" s="51"/>
+      <c r="D17" s="52"/>
+      <c r="E17" s="52"/>
+      <c r="F17" s="52"/>
+      <c r="G17" s="32"/>
+      <c r="H17" s="48"/>
+      <c r="I17" s="52" t="s">
+        <v>112</v>
+      </c>
+      <c r="J17" s="52" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="18" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C18" s="51"/>
+      <c r="D18" s="52"/>
+      <c r="E18" s="52"/>
+      <c r="F18" s="52"/>
+      <c r="G18" s="32"/>
+      <c r="H18" s="48"/>
+      <c r="I18" s="52" t="s">
+        <v>113</v>
+      </c>
+      <c r="J18" s="52" t="s">
+        <v>96</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="C4:F4"/>
+    <mergeCell ref="I4:J4"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>